--- a/assets/INDICADORES_ATs_template.xlsx
+++ b/assets/INDICADORES_ATs_template.xlsx
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>0.111</v>
+        <v>0.135</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>0.135</v>
